--- a/branches/release/v2027.0.0-ballot.rc2/ValueSet-mii-vs-lufu-sct-mef.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/ValueSet-mii-vs-lufu-sct-mef.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot.rc2/ValueSet-mii-vs-lufu-sct-mef.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/ValueSet-mii-vs-lufu-sct-mef.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
